--- a/artfynd/A 62598-2023 artfynd.xlsx
+++ b/artfynd/A 62598-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 62598-2023 artfynd.xlsx
+++ b/artfynd/A 62598-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 62598-2023 artfynd.xlsx
+++ b/artfynd/A 62598-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124667646</v>
       </c>
       <c r="B2" t="n">
-        <v>56563</v>
+        <v>56621</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
